--- a/artfynd/A 14713-2025 artfynd.xlsx
+++ b/artfynd/A 14713-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4138567</v>
+        <v>4138586</v>
       </c>
       <c r="B2" t="n">
-        <v>95528</v>
+        <v>96989</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>450011.0194529356</v>
+        <v>450011</v>
       </c>
       <c r="R2" t="n">
-        <v>6438893.219058152</v>
+        <v>6438893</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,22 +750,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1989-03-20</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1989-09-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1989-03-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1989-09-01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,6 +767,11 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Tallmo</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
@@ -785,7 +780,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Olof Janson</t>
+          <t>Gösta Börjeson, Olof Janson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">

--- a/artfynd/A 14713-2025 artfynd.xlsx
+++ b/artfynd/A 14713-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>4138586</v>
       </c>
       <c r="B2" t="n">
-        <v>96989</v>
+        <v>97157</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
